--- a/Dimensions_Lid/lid_dimensions.xlsx
+++ b/Dimensions_Lid/lid_dimensions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gtvault-my.sharepoint.com/personal/lcalimlim3_gatech_edu/Documents/Documents/GitHub/ASE6002PEK/Dimensions_Lid/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="153" documentId="8_{EB66D834-8608-4ECF-9707-3A42C7051218}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{633E4215-8537-4526-9BF5-59581CE253A7}"/>
+  <xr:revisionPtr revIDLastSave="1370" documentId="8_{EB66D834-8608-4ECF-9707-3A42C7051218}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFFF3E40-F003-4B85-B505-0F5EBE82DD72}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5D3FEB3C-2561-4B10-B57D-89B92279F071}"/>
+    <workbookView xWindow="6345" yWindow="1125" windowWidth="21570" windowHeight="11295" xr2:uid="{5D3FEB3C-2561-4B10-B57D-89B92279F071}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -468,7 +468,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>0.2</v>
+        <v>1.9998199999999999</v>
       </c>
       <c r="C3" t="s">
         <v>2</v>
@@ -479,7 +479,7 @@
         <v>10</v>
       </c>
       <c r="B4">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
         <v>2</v>
@@ -491,7 +491,7 @@
       </c>
       <c r="B5">
         <f>3.14*(diameter_lid_cm^2) * 0.25</f>
-        <v>706.5</v>
+        <v>176.625</v>
       </c>
       <c r="C5" t="s">
         <v>3</v>
@@ -514,7 +514,7 @@
       </c>
       <c r="B7">
         <f>(PI()*(diameter_lid_cm^2)*0.25)*thickness_lid*hdpe_density*hdpe_cost_per_g</f>
-        <v>6.8565259664597242</v>
+        <v>17.139772197806856</v>
       </c>
       <c r="C7" t="s">
         <v>6</v>

--- a/Dimensions_Lid/lid_dimensions.xlsx
+++ b/Dimensions_Lid/lid_dimensions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Dimensions_Lid/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1141" documentId="8_{EB66D834-8608-4ECF-9707-3A42C7051218}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A38890DF-DBFB-4E71-8F38-26C552AAD74D}"/>
+  <xr:revisionPtr revIDLastSave="1788" documentId="8_{EB66D834-8608-4ECF-9707-3A42C7051218}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F04C265C-3BB5-4759-8C48-FF394540E906}"/>
   <bookViews>
-    <workbookView xWindow="450" yWindow="2520" windowWidth="38700" windowHeight="15345" xr2:uid="{5D3FEB3C-2561-4B10-B57D-89B92279F071}"/>
+    <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{5D3FEB3C-2561-4B10-B57D-89B92279F071}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <definedName name="hdpe_density">Sheet1!$B$6</definedName>
     <definedName name="thickness_lid">Sheet1!$B$3</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcMode="manual"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -129,6 +129,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -464,7 +468,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>0.36</v>
+        <v>0.2</v>
       </c>
       <c r="C3" t="s">
         <v>2</v>
@@ -475,7 +479,7 @@
         <v>10</v>
       </c>
       <c r="B4">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
         <v>2</v>
@@ -487,7 +491,7 @@
       </c>
       <c r="B5">
         <f>3.14*(diameter_lid_cm^2) * 0.25</f>
-        <v>706.5</v>
+        <v>176.625</v>
       </c>
       <c r="C5" t="s">
         <v>3</v>
@@ -509,8 +513,8 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <f>(PI()*(diameter_lid_cm^2)*0.25)*thickness_lid*hdpe_density*hdpe_cost_per_g</f>
-        <v>12.341746739627503</v>
+        <f>area_lid*thickness_lid*hdpe_density*hdpe_cost_per_g</f>
+        <v>1.7132625000000001</v>
       </c>
       <c r="C7" t="s">
         <v>6</v>

--- a/Dimensions_Lid/lid_dimensions.xlsx
+++ b/Dimensions_Lid/lid_dimensions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gtvault-my.sharepoint.com/personal/lcalimlim3_gatech_edu/Documents/Documents/GitHub/ASE6002PEK/Dimensions_Lid/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1370" documentId="8_{EB66D834-8608-4ECF-9707-3A42C7051218}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFFF3E40-F003-4B85-B505-0F5EBE82DD72}"/>
+  <xr:revisionPtr revIDLastSave="1380" documentId="8_{EB66D834-8608-4ECF-9707-3A42C7051218}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC5922D6-44BD-4828-BC90-E785530B22AF}"/>
   <bookViews>
-    <workbookView xWindow="6345" yWindow="1125" windowWidth="21570" windowHeight="11295" xr2:uid="{5D3FEB3C-2561-4B10-B57D-89B92279F071}"/>
+    <workbookView xWindow="6255" yWindow="420" windowWidth="21570" windowHeight="11295" xr2:uid="{5D3FEB3C-2561-4B10-B57D-89B92279F071}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <definedName name="hdpe_cost_per_g">Sheet1!$B$8</definedName>
     <definedName name="hdpe_density">Sheet1!$B$6</definedName>
     <definedName name="thickness_lid">Sheet1!$B$3</definedName>
+    <definedName name="UNC_Lid_Mat_Cost">Sheet1!$B$11</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
   <si>
     <t>Lid Dimensions</t>
   </si>
@@ -77,6 +78,12 @@
   </si>
   <si>
     <t>diameter_lid_cm</t>
+  </si>
+  <si>
+    <t>UNC_Lid_Mat_Cost</t>
+  </si>
+  <si>
+    <t>% Variance</t>
   </si>
 </sst>
 </file>
@@ -452,7 +459,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60A0B59E-CC70-4DCC-800E-B087C856AC48}">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.42578125" customWidth="1"/>
@@ -468,7 +475,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>1.9998199999999999</v>
+        <v>0.2</v>
       </c>
       <c r="C3" t="s">
         <v>2</v>
@@ -479,7 +486,7 @@
         <v>10</v>
       </c>
       <c r="B4">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C4" t="s">
         <v>2</v>
@@ -491,7 +498,7 @@
       </c>
       <c r="B5">
         <f>3.14*(diameter_lid_cm^2) * 0.25</f>
-        <v>176.625</v>
+        <v>706.5</v>
       </c>
       <c r="C5" t="s">
         <v>3</v>
@@ -513,8 +520,8 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <f>(PI()*(diameter_lid_cm^2)*0.25)*thickness_lid*hdpe_density*hdpe_cost_per_g</f>
-        <v>17.139772197806856</v>
+        <f>(PI()*(diameter_lid_cm^2)*0.25)*thickness_lid*hdpe_density*hdpe_cost_per_g*B11</f>
+        <v>6.8565259664597242</v>
       </c>
       <c r="C7" t="s">
         <v>6</v>
@@ -529,6 +536,17 @@
       </c>
       <c r="C8" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/Dimensions_Lid/lid_dimensions.xlsx
+++ b/Dimensions_Lid/lid_dimensions.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gtvault-my.sharepoint.com/personal/lcalimlim3_gatech_edu/Documents/Documents/GitHub/ASE6002PEK/Dimensions_Lid/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1380" documentId="8_{EB66D834-8608-4ECF-9707-3A42C7051218}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC5922D6-44BD-4828-BC90-E785530B22AF}"/>
+  <xr:revisionPtr revIDLastSave="1402" documentId="8_{EB66D834-8608-4ECF-9707-3A42C7051218}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17CCBAB5-4EE4-400F-8D72-5FCC744F5FFD}"/>
   <bookViews>
     <workbookView xWindow="6255" yWindow="420" windowWidth="21570" windowHeight="11295" xr2:uid="{5D3FEB3C-2561-4B10-B57D-89B92279F071}"/>
   </bookViews>
@@ -21,8 +21,10 @@
     <definedName name="diameter_lid_cm">Sheet1!$B$4</definedName>
     <definedName name="hdpe_cost_per_g">Sheet1!$B$8</definedName>
     <definedName name="hdpe_density">Sheet1!$B$6</definedName>
+    <definedName name="target_thickness_lid">Sheet1!$B$2</definedName>
     <definedName name="thickness_lid">Sheet1!$B$3</definedName>
     <definedName name="UNC_Lid_Mat_Cost">Sheet1!$B$11</definedName>
+    <definedName name="UNC_Lid_Thickness">Sheet1!$B$12</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
   <si>
     <t>Lid Dimensions</t>
   </si>
@@ -84,6 +86,15 @@
   </si>
   <si>
     <t>% Variance</t>
+  </si>
+  <si>
+    <t>UNC_Lid_Thickness</t>
+  </si>
+  <si>
+    <t>target_thickness_lid</t>
+  </si>
+  <si>
+    <t>% variance</t>
   </si>
 </sst>
 </file>
@@ -459,7 +470,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60A0B59E-CC70-4DCC-800E-B087C856AC48}">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.42578125" customWidth="1"/>
@@ -470,6 +481,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2">
+        <v>0.2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2</v>
+      </c>
+    </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
@@ -547,6 +569,17 @@
       </c>
       <c r="C11" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12">
+        <v>1.05</v>
+      </c>
+      <c r="C12" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/Dimensions_Lid/lid_dimensions.xlsx
+++ b/Dimensions_Lid/lid_dimensions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gtvault-my.sharepoint.com/personal/lcalimlim3_gatech_edu/Documents/Documents/GitHub/ASE6002PEK/Dimensions_Lid/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Dimensions_Lid/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1402" documentId="8_{EB66D834-8608-4ECF-9707-3A42C7051218}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17CCBAB5-4EE4-400F-8D72-5FCC744F5FFD}"/>
+  <xr:revisionPtr revIDLastSave="42364" documentId="121_{D12FEFB8-6AB8-449E-8806-6396AAFDFD35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62880B28-BFC0-429D-B7DE-269634B95AA8}"/>
   <bookViews>
-    <workbookView xWindow="6255" yWindow="420" windowWidth="21570" windowHeight="11295" xr2:uid="{5D3FEB3C-2561-4B10-B57D-89B92279F071}"/>
+    <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{5D3FEB3C-2561-4B10-B57D-89B92279F071}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -543,7 +543,7 @@
       </c>
       <c r="B7">
         <f>(PI()*(diameter_lid_cm^2)*0.25)*thickness_lid*hdpe_density*hdpe_cost_per_g*B11</f>
-        <v>6.8565259664597242</v>
+        <v>6.7559497723649375</v>
       </c>
       <c r="C7" t="s">
         <v>6</v>
@@ -565,7 +565,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>0.98533131871930801</v>
       </c>
       <c r="C11" t="s">
         <v>12</v>
@@ -576,7 +576,7 @@
         <v>13</v>
       </c>
       <c r="B12">
-        <v>1.05</v>
+        <v>1.01044304779269</v>
       </c>
       <c r="C12" t="s">
         <v>15</v>

--- a/Dimensions_Lid/lid_dimensions.xlsx
+++ b/Dimensions_Lid/lid_dimensions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Dimensions_Lid/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42364" documentId="121_{D12FEFB8-6AB8-449E-8806-6396AAFDFD35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62880B28-BFC0-429D-B7DE-269634B95AA8}"/>
+  <xr:revisionPtr revIDLastSave="47767" documentId="121_{D12FEFB8-6AB8-449E-8806-6396AAFDFD35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DED0C13C-01B3-4B15-B975-DE7665BC59C9}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{5D3FEB3C-2561-4B10-B57D-89B92279F071}"/>
   </bookViews>
@@ -543,7 +543,7 @@
       </c>
       <c r="B7">
         <f>(PI()*(diameter_lid_cm^2)*0.25)*thickness_lid*hdpe_density*hdpe_cost_per_g*B11</f>
-        <v>6.7559497723649375</v>
+        <v>6.6864389217741769</v>
       </c>
       <c r="C7" t="s">
         <v>6</v>
@@ -565,7 +565,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>0.98533131871930801</v>
+        <v>0.97519340763564999</v>
       </c>
       <c r="C11" t="s">
         <v>12</v>
@@ -576,7 +576,7 @@
         <v>13</v>
       </c>
       <c r="B12">
-        <v>1.01044304779269</v>
+        <v>1.0025266785532201</v>
       </c>
       <c r="C12" t="s">
         <v>15</v>

--- a/Dimensions_Lid/lid_dimensions.xlsx
+++ b/Dimensions_Lid/lid_dimensions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Dimensions_Lid/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="47767" documentId="121_{D12FEFB8-6AB8-449E-8806-6396AAFDFD35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DED0C13C-01B3-4B15-B975-DE7665BC59C9}"/>
+  <xr:revisionPtr revIDLastSave="47977" documentId="121_{D12FEFB8-6AB8-449E-8806-6396AAFDFD35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2BE3B8D-8038-4A49-974E-523660CC844E}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{5D3FEB3C-2561-4B10-B57D-89B92279F071}"/>
   </bookViews>
@@ -543,7 +543,7 @@
       </c>
       <c r="B7">
         <f>(PI()*(diameter_lid_cm^2)*0.25)*thickness_lid*hdpe_density*hdpe_cost_per_g*B11</f>
-        <v>6.6864389217741769</v>
+        <v>6.4278768217359277</v>
       </c>
       <c r="C7" t="s">
         <v>6</v>
@@ -565,7 +565,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>0.97519340763564999</v>
+        <v>0.93748304216732603</v>
       </c>
       <c r="C11" t="s">
         <v>12</v>
@@ -576,7 +576,7 @@
         <v>13</v>
       </c>
       <c r="B12">
-        <v>1.0025266785532201</v>
+        <v>0.49121185088097902</v>
       </c>
       <c r="C12" t="s">
         <v>15</v>

--- a/Dimensions_Lid/lid_dimensions.xlsx
+++ b/Dimensions_Lid/lid_dimensions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Dimensions_Lid/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="47977" documentId="121_{D12FEFB8-6AB8-449E-8806-6396AAFDFD35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2BE3B8D-8038-4A49-974E-523660CC844E}"/>
+  <xr:revisionPtr revIDLastSave="50242" documentId="121_{D12FEFB8-6AB8-449E-8806-6396AAFDFD35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0CAB4AAD-3302-4E20-BAB1-D823E4560581}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{5D3FEB3C-2561-4B10-B57D-89B92279F071}"/>
   </bookViews>
@@ -543,7 +543,7 @@
       </c>
       <c r="B7">
         <f>(PI()*(diameter_lid_cm^2)*0.25)*thickness_lid*hdpe_density*hdpe_cost_per_g*B11</f>
-        <v>6.4278768217359277</v>
+        <v>6.769686120129613</v>
       </c>
       <c r="C7" t="s">
         <v>6</v>
@@ -565,7 +565,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>0.93748304216732603</v>
+        <v>0.98733471633376602</v>
       </c>
       <c r="C11" t="s">
         <v>12</v>
@@ -576,7 +576,7 @@
         <v>13</v>
       </c>
       <c r="B12">
-        <v>0.49121185088097902</v>
+        <v>0.41329796036377697</v>
       </c>
       <c r="C12" t="s">
         <v>15</v>

--- a/Dimensions_Lid/lid_dimensions.xlsx
+++ b/Dimensions_Lid/lid_dimensions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Dimensions_Lid/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="50242" documentId="121_{D12FEFB8-6AB8-449E-8806-6396AAFDFD35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0CAB4AAD-3302-4E20-BAB1-D823E4560581}"/>
+  <xr:revisionPtr revIDLastSave="57242" documentId="121_{D12FEFB8-6AB8-449E-8806-6396AAFDFD35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86302495-E424-4EE4-AE69-D12F0E40E225}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{5D3FEB3C-2561-4B10-B57D-89B92279F071}"/>
   </bookViews>
@@ -543,7 +543,7 @@
       </c>
       <c r="B7">
         <f>(PI()*(diameter_lid_cm^2)*0.25)*thickness_lid*hdpe_density*hdpe_cost_per_g*B11</f>
-        <v>6.769686120129613</v>
+        <v>6.6962978052113753</v>
       </c>
       <c r="C7" t="s">
         <v>6</v>
@@ -565,7 +565,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>0.98733471633376602</v>
+        <v>0.97663129082684996</v>
       </c>
       <c r="C11" t="s">
         <v>12</v>
@@ -576,7 +576,7 @@
         <v>13</v>
       </c>
       <c r="B12">
-        <v>0.41329796036377697</v>
+        <v>0.78015601703758497</v>
       </c>
       <c r="C12" t="s">
         <v>15</v>

--- a/Dimensions_Lid/lid_dimensions.xlsx
+++ b/Dimensions_Lid/lid_dimensions.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Dimensions_Lid/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mbail\Documents\GitHub\ASE6002PEK\Dimensions_Lid\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="57242" documentId="121_{D12FEFB8-6AB8-449E-8806-6396AAFDFD35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86302495-E424-4EE4-AE69-D12F0E40E225}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77179FFB-7334-4CE6-805D-CE9E0509C772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{5D3FEB3C-2561-4B10-B57D-89B92279F071}"/>
+    <workbookView xWindow="20325" yWindow="4995" windowWidth="14475" windowHeight="11295" xr2:uid="{5D3FEB3C-2561-4B10-B57D-89B92279F071}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -147,10 +147,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -497,7 +493,8 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>0.2</v>
+        <f>B2*(1-UNC_Lid_Thickness)</f>
+        <v>4.3968796592483012E-2</v>
       </c>
       <c r="C3" t="s">
         <v>2</v>
@@ -543,7 +540,7 @@
       </c>
       <c r="B7">
         <f>(PI()*(diameter_lid_cm^2)*0.25)*thickness_lid*hdpe_density*hdpe_cost_per_g*B11</f>
-        <v>6.6962978052113753</v>
+        <v>1.4721407806001467</v>
       </c>
       <c r="C7" t="s">
         <v>6</v>
